--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorsHoldInfoRegistdel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorsHoldInfoRegistdel.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\tamsDoubleBranch\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20736" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="投资者持有信息-批量删除" sheetId="1" r:id="rId1"/>
@@ -19,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
   <si>
     <t>版本号</t>
   </si>
@@ -668,6 +673,10 @@
     <t>**币种</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -676,7 +685,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -999,7 +1008,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1151,6 +1160,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1289,7 +1313,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1335,6 +1359,9 @@
     </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="45">
@@ -1726,14 +1753,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.125" style="3" customWidth="1" collapsed="1"/>
-    <col min="2" max="5" width="19.125" style="7" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="19.109375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="5" width="19.109375" style="7" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>188</v>
       </c>
@@ -1746,8 +1773,13 @@
       <c r="D1" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="18" t="s">
         <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -1772,923 +1804,923 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A184"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.75" style="6" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="53.77734375" style="6" customWidth="1" collapsed="1"/>
     <col min="2" max="16384" width="9" style="6" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="54" customHeight="1">
+    <row r="1" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="46.5" customHeight="1">
+    <row r="2" spans="1:1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="23.25" customHeight="1">
+    <row r="3" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="28.5">
+    <row r="4" spans="1:1" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="14.25">
+    <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="14" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="14" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="14" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="14" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="14" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="14" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="14" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="14" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="14" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="14" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="14" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="14" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="14" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="14" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="14" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="14" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="14" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="14" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="14" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="14" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="14" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="14" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="14" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="14" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="14" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="14" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="14" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="14" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="129" spans="1:1">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="14" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="14" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="132" spans="1:1">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="14" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="133" spans="1:1">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="14" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="134" spans="1:1">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="14" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="135" spans="1:1">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="136" spans="1:1">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="14" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="137" spans="1:1">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="14" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:1">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="14" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="14" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="14" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="141" spans="1:1">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="14" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="142" spans="1:1">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="14" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="143" spans="1:1">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="14" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="144" spans="1:1">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="14" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="14" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="149" spans="1:1">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="150" spans="1:1">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="14" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="151" spans="1:1">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="14" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="152" spans="1:1">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="14" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="153" spans="1:1">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="154" spans="1:1">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="14" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="155" spans="1:1">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="156" spans="1:1">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="14" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="157" spans="1:1">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="14" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="158" spans="1:1">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="14" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="159" spans="1:1">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="14" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="160" spans="1:1">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="161" spans="1:1">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="14" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="162" spans="1:1">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="14" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="163" spans="1:1">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="14" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="164" spans="1:1">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="14" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="165" spans="1:1">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="14" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="166" spans="1:1">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="14" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="167" spans="1:1">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="14" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="168" spans="1:1">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="14" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="169" spans="1:1">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="14" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="170" spans="1:1">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="14" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="171" spans="1:1">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="14" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="172" spans="1:1">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="14" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="173" spans="1:1">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="14" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="174" spans="1:1">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="14" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="175" spans="1:1">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="14" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="176" spans="1:1">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="14" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="177" spans="1:1">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="14" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="178" spans="1:1">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="14" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="179" spans="1:1">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="14" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="180" spans="1:1">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="14" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="181" spans="1:1">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="14" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="182" spans="1:1">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="14" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="183" spans="1:1">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="14" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="184" spans="1:1">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="15" t="s">
         <v>184</v>
       </c>
@@ -2703,12 +2735,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="52.875" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="52.88671875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2716,7 +2748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -2724,7 +2756,7 @@
         <v>43350</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="67.5">
+    <row r="3" spans="1:2" ht="69" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorsHoldInfoRegistdel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorsHoldInfoRegistdel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t>版本号</t>
   </si>
@@ -673,10 +673,6 @@
     <t>**币种</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
@@ -898,7 +894,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1007,26 +1003,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1186,7 +1175,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1201,7 +1190,7 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1216,28 +1205,28 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1246,10 +1235,10 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1321,15 +1310,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="22" fillId="7" borderId="5" xfId="18" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1342,16 +1326,16 @@
     <xf numFmtId="176" fontId="18" fillId="18" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1360,7 +1344,10 @@
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="19" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1753,34 +1740,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.109375" style="3" customWidth="1" collapsed="1"/>
-    <col min="2" max="5" width="19.109375" style="7" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="19.109375" style="15" customWidth="1" collapsed="1"/>
+    <col min="2" max="5" width="19.109375" style="16" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="18" t="s">
         <v>191</v>
       </c>
       <c r="E1" s="18" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>193</v>
-      </c>
+    <row r="2" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -1806,922 +1796,922 @@
   <dimension ref="A1:A184"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.77734375" style="6" customWidth="1" collapsed="1"/>
-    <col min="2" max="16384" width="9" style="6" collapsed="1"/>
+    <col min="1" max="1" width="53.77734375" style="4" customWidth="1" collapsed="1"/>
+    <col min="2" max="16384" width="9" style="4" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="13" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="14" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="14" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="11" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="11" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="11" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="11" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="11" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="11" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="11" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="11" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="11" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="11" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="11" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="11" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="11" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="11" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
+      <c r="A58" s="11" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="11" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="11" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="11" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="11" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
+      <c r="A66" s="11" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="14" t="s">
+      <c r="A67" s="11" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="14" t="s">
+      <c r="A68" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="14" t="s">
+      <c r="A69" s="11" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="14" t="s">
+      <c r="A70" s="11" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="14" t="s">
+      <c r="A71" s="11" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="11" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="14" t="s">
+      <c r="A73" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="14" t="s">
+      <c r="A74" s="11" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="14" t="s">
+      <c r="A76" s="11" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="14" t="s">
+      <c r="A77" s="11" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="11" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="11" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="14" t="s">
+      <c r="A80" s="11" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="14" t="s">
+      <c r="A81" s="11" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="14" t="s">
+      <c r="A82" s="11" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="14" t="s">
+      <c r="A83" s="11" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="14" t="s">
+      <c r="A84" s="11" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="14" t="s">
+      <c r="A85" s="11" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="14" t="s">
+      <c r="A86" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="14" t="s">
+      <c r="A87" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="11" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="14" t="s">
+      <c r="A89" s="11" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="11" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="14" t="s">
+      <c r="A91" s="11" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="14" t="s">
+      <c r="A92" s="11" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="14" t="s">
+      <c r="A93" s="11" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="14" t="s">
+      <c r="A94" s="11" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="14" t="s">
+      <c r="A95" s="11" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="14" t="s">
+      <c r="A96" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="14" t="s">
+      <c r="A97" s="11" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="14" t="s">
+      <c r="A98" s="11" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="14" t="s">
+      <c r="A99" s="11" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="14" t="s">
+      <c r="A100" s="11" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="14" t="s">
+      <c r="A101" s="11" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="14" t="s">
+      <c r="A102" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="14" t="s">
+      <c r="A103" s="11" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="14" t="s">
+      <c r="A104" s="11" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="14" t="s">
+      <c r="A105" s="11" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="14" t="s">
+      <c r="A106" s="11" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="14" t="s">
+      <c r="A107" s="11" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="14" t="s">
+      <c r="A108" s="11" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="14" t="s">
+      <c r="A109" s="11" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="14" t="s">
+      <c r="A110" s="11" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="14" t="s">
+      <c r="A111" s="11" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="14" t="s">
+      <c r="A112" s="11" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="14" t="s">
+      <c r="A113" s="11" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="14" t="s">
+      <c r="A114" s="11" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="14" t="s">
+      <c r="A115" s="11" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="14" t="s">
+      <c r="A116" s="11" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="14" t="s">
+      <c r="A117" s="11" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="14" t="s">
+      <c r="A118" s="11" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="14" t="s">
+      <c r="A119" s="11" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="14" t="s">
+      <c r="A120" s="11" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="14" t="s">
+      <c r="A121" s="11" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="14" t="s">
+      <c r="A122" s="11" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="14" t="s">
+      <c r="A123" s="11" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="14" t="s">
+      <c r="A124" s="11" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="14" t="s">
+      <c r="A125" s="11" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="14" t="s">
+      <c r="A126" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="14" t="s">
+      <c r="A127" s="11" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="14" t="s">
+      <c r="A128" s="11" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="14" t="s">
+      <c r="A129" s="11" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="14" t="s">
+      <c r="A130" s="11" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="14" t="s">
+      <c r="A131" s="11" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="14" t="s">
+      <c r="A132" s="11" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="14" t="s">
+      <c r="A133" s="11" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="14" t="s">
+      <c r="A134" s="11" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="14" t="s">
+      <c r="A135" s="11" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="14" t="s">
+      <c r="A136" s="11" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="14" t="s">
+      <c r="A137" s="11" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="14" t="s">
+      <c r="A138" s="11" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="14" t="s">
+      <c r="A139" s="11" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="14" t="s">
+      <c r="A140" s="11" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="14" t="s">
+      <c r="A141" s="11" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="14" t="s">
+      <c r="A142" s="11" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="14" t="s">
+      <c r="A143" s="11" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="14" t="s">
+      <c r="A144" s="11" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="14" t="s">
+      <c r="A145" s="11" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="14" t="s">
+      <c r="A146" s="11" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="14" t="s">
+      <c r="A147" s="11" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="14" t="s">
+      <c r="A148" s="11" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="14" t="s">
+      <c r="A149" s="11" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="14" t="s">
+      <c r="A150" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="14" t="s">
+      <c r="A151" s="11" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="14" t="s">
+      <c r="A152" s="11" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="14" t="s">
+      <c r="A153" s="11" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="14" t="s">
+      <c r="A154" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="14" t="s">
+      <c r="A155" s="11" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="14" t="s">
+      <c r="A156" s="11" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="14" t="s">
+      <c r="A157" s="11" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="14" t="s">
+      <c r="A158" s="11" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="14" t="s">
+      <c r="A159" s="11" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="14" t="s">
+      <c r="A160" s="11" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="14" t="s">
+      <c r="A161" s="11" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="14" t="s">
+      <c r="A162" s="11" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="14" t="s">
+      <c r="A163" s="11" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="14" t="s">
+      <c r="A164" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="14" t="s">
+      <c r="A165" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="14" t="s">
+      <c r="A166" s="11" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="14" t="s">
+      <c r="A167" s="11" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="14" t="s">
+      <c r="A168" s="11" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="14" t="s">
+      <c r="A169" s="11" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="14" t="s">
+      <c r="A170" s="11" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="14" t="s">
+      <c r="A171" s="11" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="14" t="s">
+      <c r="A172" s="11" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="14" t="s">
+      <c r="A173" s="11" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="14" t="s">
+      <c r="A174" s="11" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="14" t="s">
+      <c r="A175" s="11" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="14" t="s">
+      <c r="A176" s="11" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="14" t="s">
+      <c r="A177" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="14" t="s">
+      <c r="A178" s="11" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="14" t="s">
+      <c r="A179" s="11" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="14" t="s">
+      <c r="A180" s="11" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="14" t="s">
+      <c r="A181" s="11" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="14" t="s">
+      <c r="A182" s="11" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="14" t="s">
+      <c r="A183" s="11" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="15" t="s">
+      <c r="A184" s="12" t="s">
         <v>184</v>
       </c>
     </row>
@@ -2741,18 +2731,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="8">
         <v>43350</v>
       </c>
     </row>
